--- a/backtest_runs/20260410_193731/by_symbol/JLICL/JLICL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/JLICL/JLICL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-393.4500000000088</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>99606.54999999999</v>
@@ -587,7 +587,7 @@
         <v>-2063.999999999993</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>97542.55</v>
@@ -679,7 +679,7 @@
         <v>-9965.250000000011</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>89931.54999999999</v>
@@ -771,7 +771,7 @@
         <v>-1238.399999999992</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>93182.35000000001</v>
@@ -817,7 +817,7 @@
         <v>-187.0500000000132</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>92995.29999999999</v>
@@ -909,7 +909,7 @@
         <v>-2386.499999999993</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>93137.20000000001</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>93137.20000000001</v>
@@ -1047,7 +1047,7 @@
         <v>-4173.15</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>88989.85000000002</v>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>88989.85000000002</v>
@@ -1185,7 +1185,7 @@
         <v>-187.0499999999949</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>88802.80000000003</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>89551.00000000003</v>
@@ -1369,7 +1369,7 @@
         <v>-728.8500000000154</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>88822.15000000001</v>
@@ -1461,7 +1461,7 @@
         <v>-3154.05000000001</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>85668.10000000001</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>96800.80000000002</v>
